--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
+++ b/ci-build/StructureDefinition-senologie-klinische-untersuchung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3582" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="533">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: KlinischeUntersuchung</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2019,7 +2025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP92"/>
+  <dimension ref="A1:AR92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.3046875" customWidth="true" bestFit="true"/>
@@ -2057,12 +2063,14 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="41.95703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2192,6 +2200,12 @@
       <c r="AP1" t="s" s="1">
         <v>78</v>
       </c>
+      <c r="AQ1" t="s" s="1">
+        <v>79</v>
+      </c>
+      <c r="AR1" t="s" s="1">
+        <v>80</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2202,14 +2216,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2221,16 +2235,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2283,22 +2297,22 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>89</v>
@@ -2307,18 +2321,24 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AQ2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2326,10 +2346,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2338,19 +2358,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2400,13 +2420,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2430,15 +2450,21 @@
         <v>20</v>
       </c>
       <c r="AP3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2446,10 +2472,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2458,16 +2484,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2518,19 +2544,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2548,15 +2574,21 @@
         <v>20</v>
       </c>
       <c r="AP4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2564,31 +2596,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2638,19 +2670,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2668,15 +2700,21 @@
         <v>20</v>
       </c>
       <c r="AP5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2684,10 +2722,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2699,16 +2737,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2734,13 +2772,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2758,19 +2796,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2788,26 +2826,32 @@
         <v>20</v>
       </c>
       <c r="AP6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2819,16 +2863,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2878,19 +2922,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2902,32 +2946,38 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP7" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AQ7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2939,16 +2989,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2998,13 +3048,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3022,32 +3072,38 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP8" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3059,16 +3115,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3118,19 +3174,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3142,56 +3198,62 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -3240,19 +3302,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3264,21 +3326,27 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3286,10 +3354,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -3298,20 +3366,20 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3360,56 +3428,62 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
       <c r="AP11" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AQ11" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AR11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3418,20 +3492,20 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3480,56 +3554,62 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AP12" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AQ12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3538,19 +3618,19 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3600,45 +3680,51 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AQ13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3646,41 +3732,41 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>20</v>
@@ -3698,13 +3784,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3722,25 +3808,25 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>187</v>
@@ -3752,15 +3838,21 @@
         <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AQ14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AR14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3768,10 +3860,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3783,19 +3875,19 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3820,13 +3912,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3844,19 +3936,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -3868,56 +3960,62 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AQ15" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AR15" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3927,7 +4025,7 @@
         <v>20</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>20</v>
@@ -3942,13 +4040,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3966,25 +4064,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>212</v>
@@ -3997,14 +4095,20 @@
       </c>
       <c r="AP16" t="s" s="2">
         <v>215</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AR16" t="s" s="2">
+        <v>217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4012,34 +4116,34 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4088,45 +4192,51 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>225</v>
       </c>
       <c r="AP17" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AR17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4134,10 +4244,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -4146,19 +4256,19 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4208,19 +4318,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4229,35 +4339,41 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="AP18" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AQ18" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AR18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4266,22 +4382,22 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4330,56 +4446,62 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>242</v>
       </c>
       <c r="AP19" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AQ19" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AR19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -4388,22 +4510,22 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4440,92 +4562,98 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>255</v>
       </c>
       <c r="AP20" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4574,45 +4702,51 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>255</v>
       </c>
       <c r="AP21" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4620,10 +4754,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4632,19 +4766,19 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4694,19 +4828,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4715,24 +4849,30 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AR22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4740,10 +4880,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4752,20 +4892,20 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4814,45 +4954,51 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>273</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4860,10 +5006,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4872,22 +5018,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4936,45 +5082,51 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR24" t="s" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4982,10 +5134,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4997,19 +5149,19 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5034,13 +5186,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -5058,19 +5210,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -5079,35 +5231,41 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP25" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AQ25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -5119,19 +5277,19 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5156,13 +5314,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -5180,45 +5338,51 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR26" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5226,10 +5390,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5241,19 +5405,19 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5302,19 +5466,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -5323,24 +5487,30 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="AP27" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5348,13 +5518,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
@@ -5363,16 +5533,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5398,13 +5568,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5422,45 +5592,51 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>326</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR28" t="s" s="2">
+        <v>329</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5468,10 +5644,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5483,13 +5659,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5540,13 +5716,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -5564,32 +5740,38 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5601,16 +5783,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5648,31 +5830,31 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5684,21 +5866,27 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5706,10 +5894,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5718,22 +5906,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5758,11 +5946,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5780,19 +5968,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5801,24 +5989,30 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AP31" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AQ31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5826,10 +6020,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5838,22 +6032,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5902,19 +6096,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5923,24 +6117,30 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>356</v>
+        <v>20</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="AP32" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5948,10 +6148,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5963,19 +6163,19 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -6000,13 +6200,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -6024,19 +6224,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -6045,24 +6245,30 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="AP33" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6070,10 +6276,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6085,16 +6291,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6144,45 +6350,51 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>373</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR34" t="s" s="2">
+        <v>376</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6190,10 +6402,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6205,16 +6417,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6264,45 +6476,51 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>382</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
+      </c>
+      <c r="AQ35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR35" t="s" s="2">
+        <v>385</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6310,10 +6528,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6325,19 +6543,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6386,19 +6604,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6407,24 +6625,30 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AP36" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6432,10 +6656,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6447,13 +6671,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6504,13 +6728,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -6528,32 +6752,38 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6565,16 +6795,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6624,19 +6854,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6648,56 +6878,62 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP38" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6746,19 +6982,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6770,21 +7006,27 @@
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6792,10 +7034,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6807,13 +7049,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6864,19 +7106,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6885,24 +7127,30 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>405</v>
+        <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="AP40" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AQ40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6910,10 +7158,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6925,13 +7173,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6982,45 +7230,51 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AP41" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7028,10 +7282,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -7043,19 +7297,19 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7080,13 +7334,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -7104,45 +7358,51 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>308</v>
+        <v>420</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="AP42" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7150,10 +7410,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7165,19 +7425,19 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7202,13 +7462,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7226,45 +7486,51 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="AO43" t="s" s="2">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="AP43" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AQ43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7272,10 +7538,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -7287,17 +7553,17 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7346,19 +7612,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7370,21 +7636,27 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP44" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AQ44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7392,10 +7664,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7407,13 +7679,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7464,19 +7736,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7485,24 +7757,30 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>405</v>
+        <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>436</v>
+        <v>20</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="AP45" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7510,10 +7788,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7522,19 +7800,19 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7584,19 +7862,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7605,24 +7883,30 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="AP46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7630,10 +7914,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7642,19 +7926,19 @@
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7704,45 +7988,51 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AP47" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7750,34 +8040,34 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7814,29 +8104,29 @@
         <v>20</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7845,24 +8135,30 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>457</v>
+        <v>20</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="AP48" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7870,10 +8166,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7885,13 +8181,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7942,13 +8238,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7966,32 +8262,38 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP49" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8003,16 +8305,16 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8062,19 +8364,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8086,56 +8388,62 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP50" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8184,19 +8492,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8208,21 +8516,27 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8230,10 +8544,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8242,22 +8556,22 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8282,13 +8596,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8306,45 +8620,51 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>213</v>
+        <v>467</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP52" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8352,10 +8672,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -8364,22 +8684,22 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8428,45 +8748,51 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>469</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>286</v>
+        <v>471</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR53" t="s" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8474,10 +8800,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8489,19 +8815,19 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8526,13 +8852,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8550,19 +8876,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8571,35 +8897,41 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP54" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR54" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8611,19 +8943,19 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8648,13 +8980,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8672,45 +9004,51 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>308</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR55" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8718,10 +9056,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8733,19 +9071,19 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8794,19 +9132,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8815,61 +9153,67 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AP56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8918,19 +9262,19 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8939,24 +9283,30 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>457</v>
+        <v>20</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="AP57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR57" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8964,10 +9314,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -8979,13 +9329,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9036,13 +9386,13 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
@@ -9060,32 +9410,38 @@
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR58" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9097,16 +9453,16 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9156,19 +9512,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9180,56 +9536,62 @@
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR59" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9278,19 +9640,19 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
@@ -9302,21 +9664,27 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9324,10 +9692,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9336,22 +9704,22 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9361,7 +9729,7 @@
         <v>20</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>20</v>
@@ -9376,13 +9744,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9400,45 +9768,51 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>213</v>
+        <v>467</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AR61" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9446,10 +9820,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9458,22 +9832,22 @@
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9522,45 +9896,51 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>469</v>
+        <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>286</v>
+        <v>471</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9568,10 +9948,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9583,19 +9963,19 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9620,13 +10000,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9644,19 +10024,19 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -9665,35 +10045,41 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP63" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR63" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9705,19 +10091,19 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9742,13 +10128,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9766,45 +10152,51 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>308</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9812,10 +10204,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9827,19 +10219,19 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9888,19 +10280,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -9909,61 +10301,67 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AP65" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR65" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10012,19 +10410,19 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10033,24 +10431,30 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>457</v>
+        <v>20</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="AP66" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR66" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10058,10 +10462,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -10073,13 +10477,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10130,13 +10534,13 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
@@ -10154,32 +10558,38 @@
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP67" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR67" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -10191,16 +10601,16 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10250,19 +10660,19 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
@@ -10274,56 +10684,62 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP68" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10372,19 +10788,19 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -10396,21 +10812,27 @@
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP69" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10418,10 +10840,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10430,22 +10852,22 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10455,7 +10877,7 @@
         <v>20</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>20</v>
@@ -10470,13 +10892,13 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10494,45 +10916,51 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>213</v>
+        <v>467</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP70" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10540,10 +10968,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10552,22 +10980,22 @@
         <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10616,45 +11044,51 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>469</v>
+        <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>286</v>
+        <v>471</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10662,10 +11096,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -10677,19 +11111,19 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10714,13 +11148,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10738,19 +11172,19 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10759,35 +11193,41 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP72" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10799,19 +11239,19 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10836,13 +11276,13 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -10860,45 +11300,51 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>308</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10906,10 +11352,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10921,19 +11367,19 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10982,19 +11428,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -11003,61 +11449,67 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AP74" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR74" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11106,19 +11558,19 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -11127,24 +11579,30 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>457</v>
+        <v>20</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="AP75" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11152,10 +11610,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -11167,13 +11625,13 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11224,13 +11682,13 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
@@ -11248,32 +11706,38 @@
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP76" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR76" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -11285,16 +11749,16 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11344,19 +11808,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11368,56 +11832,62 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP77" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR77" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11466,19 +11936,19 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -11490,21 +11960,27 @@
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP78" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11512,10 +11988,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -11524,22 +12000,22 @@
         <v>20</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11549,7 +12025,7 @@
         <v>20</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>20</v>
@@ -11564,13 +12040,13 @@
         <v>20</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -11588,45 +12064,51 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>213</v>
+        <v>467</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP79" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AR79" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11634,10 +12116,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -11646,22 +12128,22 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11710,45 +12192,51 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>469</v>
+        <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>286</v>
+        <v>471</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR80" t="s" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11756,10 +12244,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -11771,19 +12259,19 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11808,13 +12296,13 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -11832,19 +12320,19 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -11853,35 +12341,41 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP81" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR81" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -11893,19 +12387,19 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -11930,13 +12424,13 @@
         <v>20</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -11954,45 +12448,51 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>308</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR82" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12000,10 +12500,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -12015,19 +12515,19 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12076,19 +12576,19 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
@@ -12097,61 +12597,67 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AP83" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR83" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12200,19 +12706,19 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
@@ -12221,24 +12727,30 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>456</v>
+        <v>20</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>457</v>
+        <v>20</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="AP84" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12246,10 +12758,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
@@ -12261,13 +12773,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12318,13 +12830,13 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
@@ -12342,32 +12854,38 @@
         <v>20</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP85" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR85" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -12379,16 +12897,16 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12438,19 +12956,19 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>20</v>
@@ -12462,56 +12980,62 @@
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP86" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR86" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12560,19 +13084,19 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
@@ -12584,21 +13108,27 @@
         <v>20</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP87" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR87" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12606,10 +13136,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
@@ -12618,22 +13148,22 @@
         <v>20</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12643,7 +13173,7 @@
         <v>20</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>20</v>
@@ -12658,13 +13188,13 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12682,45 +13212,51 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>465</v>
+        <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>213</v>
+        <v>467</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>214</v>
       </c>
       <c r="AP88" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AR88" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12728,10 +13264,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>20</v>
@@ -12740,22 +13276,22 @@
         <v>20</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12804,45 +13340,51 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>469</v>
+        <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>286</v>
+        <v>471</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR89" t="s" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12850,10 +13392,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -12865,19 +13407,19 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12902,13 +13444,13 @@
         <v>20</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
@@ -12926,19 +13468,19 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
@@ -12947,35 +13489,41 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AP90" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AQ90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR90" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -12987,19 +13535,19 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13024,13 +13572,13 @@
         <v>20</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -13048,45 +13596,51 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>306</v>
+        <v>20</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>308</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR91" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13094,10 +13648,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
@@ -13109,19 +13663,19 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13170,19 +13724,19 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>20</v>
@@ -13191,20 +13745,26 @@
         <v>20</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AP92" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR92" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP92">
+  <autoFilter ref="A1:AR92">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
